--- a/examples/phase/y-maze/result/y_maze.xlsx
+++ b/examples/phase/y-maze/result/y_maze.xlsx
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>26.31578947368421</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N4" t="n">
         <v>35.2</v>
@@ -735,7 +735,7 @@
         <v>354.8666666666667</v>
       </c>
       <c r="T4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
         <v>6</v>
@@ -744,13 +744,13 @@
         <v>4</v>
       </c>
       <c r="W4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="n">
         <v>2</v>
@@ -762,10 +762,10 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE4" t="n">
         <v>10.68525384314066</v>
@@ -822,7 +822,7 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>31.57894736842105</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="N5" t="n">
         <v>7.75</v>
@@ -846,16 +846,16 @@
         <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V5" t="n">
         <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -867,13 +867,13 @@
         <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>8.314344408691291</v>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>33.33333333333334</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="N6" t="n">
         <v>0.5714285714285714</v>
@@ -950,13 +950,13 @@
         <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V6" t="n">
         <v>3</v>
       </c>
       <c r="W6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>25.80645161290322</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N7" t="n">
         <v>21</v>
@@ -1058,16 +1058,16 @@
         <v>7</v>
       </c>
       <c r="U7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W7" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1076,16 +1076,16 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
         <v>11.81104499857549</v>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>8.571428571428571</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="N8" t="n">
         <v>18.07142857142857</v>
@@ -1159,7 +1159,7 @@
         <v>373.0714285714286</v>
       </c>
       <c r="T8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U8" t="n">
         <v>6</v>
@@ -1168,28 +1168,28 @@
         <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z8" t="n">
         <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
         <v>1</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AE8" t="n">
         <v>13.7125043495322</v>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>11.76470588235294</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N9" t="n">
         <v>36.75</v>
@@ -1267,37 +1267,37 @@
         <v>367.4166666666666</v>
       </c>
       <c r="T9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V9" t="n">
         <v>5</v>
       </c>
       <c r="W9" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
         <v>11.13030763404242</v>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>16.66666666666667</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="N10" t="n">
         <v>9.928571428571429</v>
@@ -1371,19 +1371,19 @@
         <v>378.2857142857143</v>
       </c>
       <c r="T10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V10" t="n">
         <v>8</v>
       </c>
       <c r="W10" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="n">
         <v>1</v>
@@ -1392,16 +1392,16 @@
         <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
         <v>15.60622376770538</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>15.78947368421053</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="N11" t="n">
         <v>50.08333333333334</v>
@@ -1482,13 +1482,13 @@
         <v>10</v>
       </c>
       <c r="U11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="X11" t="n">
         <v>1</v>
@@ -1497,19 +1497,19 @@
         <v>1</v>
       </c>
       <c r="Z11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC11" t="n">
         <v>1</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
         <v>14.12624982217928</v>
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>35.71428571428572</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N12" t="n">
         <v>12.57142857142857</v>
@@ -1583,16 +1583,16 @@
         <v>383</v>
       </c>
       <c r="T12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V12" t="n">
         <v>12</v>
       </c>
       <c r="W12" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="X12" t="n">
         <v>3</v>
@@ -1604,16 +1604,16 @@
         <v>3</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AE12" t="n">
         <v>19.53168444063665</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>17.94871794871795</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N13" t="n">
         <v>22.41666666666667</v>
@@ -1691,37 +1691,37 @@
         <v>367.6666666666666</v>
       </c>
       <c r="T13" t="n">
+        <v>9</v>
+      </c>
+      <c r="U13" t="n">
+        <v>9</v>
+      </c>
+      <c r="V13" t="n">
         <v>10</v>
       </c>
-      <c r="U13" t="n">
-        <v>10</v>
-      </c>
-      <c r="V13" t="n">
-        <v>9</v>
-      </c>
       <c r="W13" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD13" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
         <v>16.08012399039713</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>14.28571428571429</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N14" t="n">
         <v>7.357142857142857</v>
@@ -1795,16 +1795,16 @@
         <v>381.2857142857143</v>
       </c>
       <c r="T14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
         <v>4</v>
       </c>
       <c r="W14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1816,16 +1816,16 @@
         <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
         <v>9.432762345924253</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>41.66666666666666</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N15" t="n">
         <v>5.2</v>
@@ -1906,34 +1906,34 @@
         <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V15" t="n">
         <v>4</v>
       </c>
       <c r="W15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
         <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA15" t="n">
         <v>1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC15" t="n">
         <v>1</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>6.921094666217171</v>
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>18.42105263157895</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N16" t="n">
         <v>19.26666666666667</v>
@@ -2010,22 +2010,22 @@
         <v>7</v>
       </c>
       <c r="U16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2034,10 +2034,10 @@
         <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE16" t="n">
         <v>11.77907309191594</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>38.46153846153846</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N17" t="n">
         <v>41.7</v>
@@ -2118,34 +2118,34 @@
         <v>9</v>
       </c>
       <c r="U17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V17" t="n">
         <v>7</v>
       </c>
       <c r="W17" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA17" t="n">
         <v>1</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC17" t="n">
         <v>3</v>
       </c>
       <c r="AD17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
         <v>10.41095416113436</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>15</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N18" t="n">
         <v>6.714285714285714</v>
@@ -2222,34 +2222,34 @@
         <v>4</v>
       </c>
       <c r="U18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V18" t="n">
         <v>5</v>
       </c>
       <c r="W18" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z18" t="n">
         <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE18" t="n">
         <v>10.09791873607093</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>15.625</v>
+        <v>65</v>
       </c>
       <c r="N19" t="n">
         <v>13.28571428571429</v>
@@ -2327,37 +2327,37 @@
         <v>379.5</v>
       </c>
       <c r="T19" t="n">
+        <v>6</v>
+      </c>
+      <c r="U19" t="n">
         <v>8</v>
-      </c>
-      <c r="U19" t="n">
-        <v>9</v>
       </c>
       <c r="V19" t="n">
         <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="n">
         <v>1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
         <v>12.90111790721274</v>
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>15.21739130434783</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N20" t="n">
         <v>24.5</v>
@@ -2437,31 +2437,31 @@
         <v>12</v>
       </c>
       <c r="V20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W20" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD20" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE20" t="n">
         <v>15.74763292187384</v>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>20</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="N21" t="n">
         <v>11.92857142857143</v>
@@ -2545,31 +2545,31 @@
         <v>10</v>
       </c>
       <c r="V21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W21" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
         <v>1</v>
       </c>
       <c r="Z21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
         <v>14.49246238121175</v>
@@ -2622,7 +2622,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>33.80281690140845</v>
+        <v>70.37037037037037</v>
       </c>
       <c r="N22" t="n">
         <v>16.21428571428572</v>
@@ -2646,16 +2646,16 @@
         <v>20</v>
       </c>
       <c r="U22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="V22" t="n">
         <v>17</v>
       </c>
       <c r="W22" t="n">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="X22" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -2664,16 +2664,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AB22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD22" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AE22" t="n">
         <v>28.51562731119785</v>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>15.94202898550725</v>
+        <v>58.53658536585366</v>
       </c>
       <c r="N23" t="n">
         <v>50.07142857142857</v>
@@ -2751,37 +2751,37 @@
         <v>382.2857142857142</v>
       </c>
       <c r="T23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U23" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="V23" t="n">
         <v>12</v>
       </c>
       <c r="W23" t="n">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="X23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AB23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AE23" t="n">
         <v>23.10999327096483</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>43.75</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N24" t="n">
         <v>1</v>
@@ -2855,7 +2855,7 @@
         <v>382.2857142857143</v>
       </c>
       <c r="T24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
         <v>7</v>
@@ -2864,7 +2864,7 @@
         <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="X24" t="n">
         <v>2</v>
@@ -2882,10 +2882,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE24" t="n">
         <v>9.421692039238483</v>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
-        <v>24.13793103448276</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="N25" t="n">
         <v>16.73333333333333</v>
@@ -2963,19 +2963,19 @@
         <v>356.9333333333333</v>
       </c>
       <c r="T25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U25" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V25" t="n">
         <v>7</v>
       </c>
       <c r="W25" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y25" t="n">
         <v>1</v>
@@ -2987,13 +2987,13 @@
         <v>3</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE25" t="n">
         <v>16.08627961600177</v>
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>21.05263157894737</v>
+        <v>81.81818181818181</v>
       </c>
       <c r="N26" t="n">
         <v>13.57142857142857</v>
@@ -3067,25 +3067,25 @@
         <v>380.5714285714286</v>
       </c>
       <c r="T26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V26" t="n">
         <v>4</v>
       </c>
       <c r="W26" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
         <v>2</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA26" t="n">
         <v>1</v>
@@ -3094,10 +3094,10 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE26" t="n">
         <v>10.63572273625703</v>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
-        <v>14.28571428571429</v>
+        <v>68.75</v>
       </c>
       <c r="N27" t="n">
         <v>62.07142857142857</v>
@@ -3178,34 +3178,34 @@
         <v>5</v>
       </c>
       <c r="U27" t="n">
+        <v>6</v>
+      </c>
+      <c r="V27" t="n">
         <v>7</v>
       </c>
-      <c r="V27" t="n">
-        <v>8</v>
-      </c>
       <c r="W27" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AE27" t="n">
         <v>11.09705654644747</v>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>37.5</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N28" t="n">
         <v>8.642857142857142</v>
@@ -3285,10 +3285,10 @@
         <v>5</v>
       </c>
       <c r="V28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W28" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="X28" t="n">
         <v>2</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
-        <v>21.73913043478261</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="N29" t="n">
         <v>5.571428571428571</v>
@@ -3390,34 +3390,34 @@
         <v>6</v>
       </c>
       <c r="U29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V29" t="n">
         <v>7</v>
       </c>
       <c r="W29" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="X29" t="n">
         <v>2</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="n">
         <v>2</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE29" t="n">
         <v>12.24127086112688</v>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>13.04347826086956</v>
+        <v>43.75</v>
       </c>
       <c r="N30" t="n">
         <v>5.714285714285714</v>
@@ -3491,7 +3491,7 @@
         <v>380.4285714285714</v>
       </c>
       <c r="T30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U30" t="n">
         <v>4</v>
@@ -3500,28 +3500,28 @@
         <v>6</v>
       </c>
       <c r="W30" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA30" t="n">
         <v>1</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
         <v>14.25501913223061</v>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
-        <v>11.11111111111111</v>
+        <v>43.75</v>
       </c>
       <c r="N31" t="n">
         <v>9.571428571428571</v>
@@ -3602,22 +3602,22 @@
         <v>5</v>
       </c>
       <c r="U31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W31" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="X31" t="n">
         <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD31" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE31" t="n">
         <v>11.54784218870306</v>
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>7.142857142857143</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N32" t="n">
         <v>18</v>
@@ -3706,34 +3706,34 @@
         <v>6</v>
       </c>
       <c r="U32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V32" t="n">
         <v>5</v>
       </c>
       <c r="W32" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="X32" t="n">
         <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA32" t="n">
         <v>1</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD32" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AE32" t="n">
         <v>11.41515003540608</v>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
-        <v>6.976744186046512</v>
+        <v>56</v>
       </c>
       <c r="N33" t="n">
         <v>63.14285714285715</v>
@@ -3811,37 +3811,37 @@
         <v>372.4285714285714</v>
       </c>
       <c r="T33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U33" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W33" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD33" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AE33" t="n">
         <v>15.23534653297857</v>
@@ -3894,7 +3894,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>44.44444444444444</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
@@ -3918,22 +3918,22 @@
         <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V34" t="n">
         <v>3</v>
       </c>
       <c r="W34" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -3945,7 +3945,7 @@
         <v>2</v>
       </c>
       <c r="AD34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE34" t="n">
         <v>7.05345052666358</v>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="N35" t="n">
         <v>8.714285714285714</v>
@@ -4023,37 +4023,37 @@
         <v>379.9285714285714</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
         <v>3</v>
       </c>
       <c r="V35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W35" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE35" t="n">
         <v>8.412329661306924</v>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>15.78947368421053</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N36" t="n">
         <v>4.571428571428571</v>
@@ -4133,31 +4133,31 @@
         <v>4</v>
       </c>
       <c r="V36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W36" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y36" t="n">
         <v>1</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD36" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE36" t="n">
         <v>14.57107536811545</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
-        <v>14.28571428571429</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="N37" t="n">
         <v>12.28571428571429</v>
@@ -4238,34 +4238,34 @@
         <v>4</v>
       </c>
       <c r="U37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V37" t="n">
         <v>7</v>
       </c>
       <c r="W37" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD37" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AE37" t="n">
         <v>10.2592507253166</v>
@@ -4318,7 +4318,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>46.15384615384615</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N38" t="n">
         <v>2.642857142857143</v>
@@ -4345,16 +4345,16 @@
         <v>5</v>
       </c>
       <c r="V38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W38" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z38" t="n">
         <v>3</v>
@@ -4369,7 +4369,7 @@
         <v>2</v>
       </c>
       <c r="AD38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE38" t="n">
         <v>8.475321931532404</v>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
-        <v>3.225806451612903</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N39" t="n">
         <v>53.28571428571428</v>
@@ -4453,31 +4453,31 @@
         <v>6</v>
       </c>
       <c r="V39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W39" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC39" t="n">
         <v>1</v>
       </c>
       <c r="AD39" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AE39" t="n">
         <v>10.52061300450161</v>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>2.857142857142857</v>
+        <v>65</v>
       </c>
       <c r="N40" t="n">
         <v>19.28571428571428</v>
@@ -4554,34 +4554,34 @@
         <v>6</v>
       </c>
       <c r="U40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W40" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD40" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AE40" t="n">
         <v>15.69465157556373</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
-        <v>18.75</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N41" t="n">
         <v>37.5</v>
@@ -4659,19 +4659,19 @@
         <v>377.6428571428571</v>
       </c>
       <c r="T41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V41" t="n">
         <v>3</v>
       </c>
       <c r="W41" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -4683,13 +4683,13 @@
         <v>2</v>
       </c>
       <c r="AB41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE41" t="n">
         <v>7.80333166887733</v>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>24.24242424242424</v>
+        <v>54.16666666666666</v>
       </c>
       <c r="N42" t="n">
         <v>16.78571428571428</v>
@@ -4766,34 +4766,34 @@
         <v>7</v>
       </c>
       <c r="U42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V42" t="n">
         <v>10</v>
       </c>
       <c r="W42" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA42" t="n">
         <v>2</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC42" t="n">
         <v>2</v>
       </c>
       <c r="AD42" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE42" t="n">
         <v>14.63866349979656</v>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
-        <v>20.51282051282051</v>
+        <v>59.25925925925926</v>
       </c>
       <c r="N43" t="n">
         <v>26.28571428571428</v>
@@ -4874,34 +4874,34 @@
         <v>9</v>
       </c>
       <c r="U43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W43" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="X43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD43" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AE43" t="n">
         <v>15.12950292903248</v>
@@ -4954,7 +4954,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>8.333333333333334</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N44" t="n">
         <v>19.28571428571428</v>
@@ -4975,7 +4975,7 @@
         <v>380.7142857142857</v>
       </c>
       <c r="T44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U44" t="n">
         <v>6</v>
@@ -4984,28 +4984,28 @@
         <v>7</v>
       </c>
       <c r="W44" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="X44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD44" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AE44" t="n">
         <v>12.1891690979476</v>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N45" t="n">
         <v>50.28571428571428</v>
@@ -5089,31 +5089,31 @@
         <v>5</v>
       </c>
       <c r="V45" t="n">
+        <v>7</v>
+      </c>
+      <c r="W45" t="n">
+        <v>14</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD45" t="n">
         <v>8</v>
-      </c>
-      <c r="W45" t="n">
-        <v>24</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
       </c>
       <c r="AE45" t="n">
         <v>11.27557106231012</v>
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>7.936507936507937</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N46" t="n">
         <v>66.5</v>
@@ -5187,37 +5187,37 @@
         <v>379.0714285714286</v>
       </c>
       <c r="T46" t="n">
+        <v>10</v>
+      </c>
+      <c r="U46" t="n">
+        <v>13</v>
+      </c>
+      <c r="V46" t="n">
         <v>12</v>
       </c>
-      <c r="U46" t="n">
-        <v>16</v>
-      </c>
-      <c r="V46" t="n">
-        <v>14</v>
-      </c>
       <c r="W46" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y46" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Z46" t="n">
         <v>3</v>
       </c>
       <c r="AA46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD46" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="AE46" t="n">
         <v>19.84661349227266</v>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
-        <v>18.42105263157895</v>
+        <v>60</v>
       </c>
       <c r="N47" t="n">
         <v>42.57142857142857</v>
@@ -5295,37 +5295,37 @@
         <v>382.1428571428571</v>
       </c>
       <c r="T47" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U47" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V47" t="n">
         <v>9</v>
       </c>
       <c r="W47" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="X47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y47" t="n">
         <v>1</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD47" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AE47" t="n">
         <v>14.0340631427419</v>
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>9.523809523809524</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N48" t="n">
         <v>20.64285714285714</v>
@@ -5402,34 +5402,34 @@
         <v>6</v>
       </c>
       <c r="U48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V48" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W48" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="X48" t="n">
         <v>1</v>
       </c>
       <c r="Y48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB48" t="n">
         <v>1</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD48" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AE48" t="n">
         <v>14.78361495343927</v>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
-        <v>21.21212121212121</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N49" t="n">
         <v>89.07142857142857</v>
@@ -5507,37 +5507,37 @@
         <v>383.3571428571429</v>
       </c>
       <c r="T49" t="n">
+        <v>6</v>
+      </c>
+      <c r="U49" t="n">
         <v>7</v>
       </c>
-      <c r="U49" t="n">
-        <v>8</v>
-      </c>
       <c r="V49" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W49" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="X49" t="n">
         <v>2</v>
       </c>
       <c r="Y49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD49" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE49" t="n">
         <v>13.92246079007708</v>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>11.62790697674419</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N50" t="n">
         <v>29.85714285714286</v>
@@ -5617,31 +5617,31 @@
         <v>12</v>
       </c>
       <c r="V50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W50" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="X50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y50" t="n">
         <v>1</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD50" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="AE50" t="n">
         <v>19.12977425740753</v>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
-        <v>16.66666666666667</v>
+        <v>68.75</v>
       </c>
       <c r="N51" t="n">
         <v>14.5</v>
@@ -5719,37 +5719,37 @@
         <v>382.2142857142857</v>
       </c>
       <c r="T51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V51" t="n">
         <v>6</v>
       </c>
       <c r="W51" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD51" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AE51" t="n">
         <v>10.05502207197916</v>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>20</v>
+        <v>61.29032258064516</v>
       </c>
       <c r="N52" t="n">
         <v>55.85714285714285</v>
@@ -5823,7 +5823,7 @@
         <v>377.0714285714286</v>
       </c>
       <c r="T52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U52" t="n">
         <v>14</v>
@@ -5832,28 +5832,28 @@
         <v>10</v>
       </c>
       <c r="W52" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB52" t="n">
         <v>1</v>
       </c>
       <c r="AC52" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD52" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AE52" t="n">
         <v>18.32968508628318</v>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
-        <v>21.05263157894737</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N53" t="n">
         <v>80.71428571428571</v>
@@ -5934,34 +5934,34 @@
         <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V53" t="n">
         <v>5</v>
       </c>
       <c r="W53" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD53" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE53" t="n">
         <v>9.122994374862644</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>7.692307692307693</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="N54" t="n">
         <v>154.0714285714286</v>
@@ -6035,37 +6035,37 @@
         <v>370.2857142857143</v>
       </c>
       <c r="T54" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U54" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V54" t="n">
         <v>7</v>
       </c>
       <c r="W54" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="X54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD54" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AE54" t="n">
         <v>13.3526966055119</v>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="n">
-        <v>14.28571428571429</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="N55" t="n">
         <v>17.06666666666667</v>
@@ -6143,7 +6143,7 @@
         <v>352.1333333333333</v>
       </c>
       <c r="T55" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U55" t="n">
         <v>9</v>
@@ -6152,7 +6152,7 @@
         <v>7</v>
       </c>
       <c r="W55" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="X55" t="n">
         <v>2</v>
@@ -6161,19 +6161,19 @@
         <v>1</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD55" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE55" t="n">
         <v>13.5452887898638</v>
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>12.5</v>
+        <v>65</v>
       </c>
       <c r="N56" t="n">
         <v>71.28571428571429</v>
@@ -6250,34 +6250,34 @@
         <v>6</v>
       </c>
       <c r="U56" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V56" t="n">
         <v>9</v>
       </c>
       <c r="W56" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y56" t="n">
         <v>1</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD56" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AE56" t="n">
         <v>14.30606907568345</v>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="n">
-        <v>46.15384615384615</v>
+        <v>60</v>
       </c>
       <c r="N57" t="n">
         <v>47</v>
@@ -6364,7 +6364,7 @@
         <v>5</v>
       </c>
       <c r="W57" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="X57" t="n">
         <v>2</v>
@@ -6379,10 +6379,10 @@
         <v>1</v>
       </c>
       <c r="AB57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD57" t="n">
         <v>6</v>
@@ -6438,7 +6438,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>11.36363636363636</v>
+        <v>50</v>
       </c>
       <c r="N58" t="n">
         <v>21.42857142857143</v>
@@ -6462,16 +6462,16 @@
         <v>8</v>
       </c>
       <c r="U58" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W58" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="X58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y58" t="n">
         <v>1</v>
@@ -6480,16 +6480,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD58" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE58" t="n">
         <v>14.22609601884384</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
-        <v>12.96296296296296</v>
+        <v>67.64705882352941</v>
       </c>
       <c r="N59" t="n">
         <v>69.07142857142857</v>
@@ -6567,37 +6567,37 @@
         <v>379.2142857142857</v>
       </c>
       <c r="T59" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U59" t="n">
+        <v>11</v>
+      </c>
+      <c r="V59" t="n">
         <v>12</v>
       </c>
-      <c r="V59" t="n">
-        <v>13</v>
-      </c>
       <c r="W59" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="X59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB59" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD59" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AE59" t="n">
         <v>18.73718650257192</v>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
-        <v>10.71428571428571</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N60" t="n">
         <v>17.57142857142857</v>
@@ -6678,34 +6678,34 @@
         <v>8</v>
       </c>
       <c r="U60" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V60" t="n">
         <v>6</v>
       </c>
       <c r="W60" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="X60" t="n">
         <v>1</v>
       </c>
       <c r="Y60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z60" t="n">
         <v>1</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AE60" t="n">
         <v>11.26623517489675</v>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
-        <v>25</v>
+        <v>47.61904761904762</v>
       </c>
       <c r="N61" t="n">
         <v>12.28571428571429</v>
@@ -6783,37 +6783,37 @@
         <v>384.0714285714286</v>
       </c>
       <c r="T61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U61" t="n">
         <v>9</v>
       </c>
       <c r="V61" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W61" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="X61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y61" t="n">
         <v>1</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA61" t="n">
         <v>2</v>
       </c>
       <c r="AB61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD61" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE61" t="n">
         <v>12.15009734191931</v>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
-        <v>8.333333333333334</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N62" t="n">
         <v>24.78571428571428</v>
@@ -6891,25 +6891,25 @@
         <v>381.8571428571429</v>
       </c>
       <c r="T62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U62" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V62" t="n">
         <v>5</v>
       </c>
       <c r="W62" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -6918,10 +6918,10 @@
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD62" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE62" t="n">
         <v>10.0659504362107</v>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="n">
-        <v>17.14285714285714</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N63" t="n">
         <v>23.14285714285714</v>
@@ -7002,34 +7002,34 @@
         <v>7</v>
       </c>
       <c r="U63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W63" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="X63" t="n">
         <v>1</v>
       </c>
       <c r="Y63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC63" t="n">
         <v>1</v>
       </c>
       <c r="AD63" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE63" t="n">
         <v>12.99407667651426</v>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="n">
-        <v>13.88888888888889</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N64" t="n">
         <v>153.4285714285714</v>
@@ -7107,16 +7107,16 @@
         <v>367.8571428571429</v>
       </c>
       <c r="T64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U64" t="n">
         <v>7</v>
       </c>
       <c r="V64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W64" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="X64" t="n">
         <v>1</v>
@@ -7125,19 +7125,19 @@
         <v>2</v>
       </c>
       <c r="Z64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD64" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE64" t="n">
         <v>13.08987269193913</v>
@@ -7221,10 +7221,10 @@
         <v>3</v>
       </c>
       <c r="V65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W65" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X65" t="n">
         <v>0</v>
@@ -7242,10 +7242,10 @@
         <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE65" t="n">
         <v>6.862650950975212</v>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
-        <v>49.6551724137931</v>
+        <v>53.9568345323741</v>
       </c>
       <c r="N66" t="n">
         <v>0.3571428571428572</v>
@@ -7326,19 +7326,19 @@
         <v>52</v>
       </c>
       <c r="U66" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="V66" t="n">
         <v>44</v>
       </c>
       <c r="W66" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="X66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y66" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z66" t="n">
         <v>19</v>
@@ -7350,10 +7350,10 @@
         <v>6</v>
       </c>
       <c r="AC66" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD66" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AE66" t="n">
         <v>68.70931056909436</v>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="n">
-        <v>80.74074074074075</v>
+        <v>81.20300751879699</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -7431,7 +7431,7 @@
         <v>382.9285714285714</v>
       </c>
       <c r="T67" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U67" t="n">
         <v>46</v>
@@ -7440,13 +7440,13 @@
         <v>45</v>
       </c>
       <c r="W67" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="X67" t="n">
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z67" t="n">
         <v>35</v>
@@ -7461,7 +7461,7 @@
         <v>36</v>
       </c>
       <c r="AD67" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE67" t="n">
         <v>54.76665310164869</v>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="n">
-        <v>38.09523809523809</v>
+        <v>71.875</v>
       </c>
       <c r="N68" t="n">
         <v>15</v>
@@ -7539,25 +7539,25 @@
         <v>388</v>
       </c>
       <c r="T68" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="U68" t="n">
         <v>10</v>
       </c>
       <c r="V68" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W68" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="X68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y68" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z68" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AA68" t="n">
         <v>1</v>
@@ -7569,7 +7569,7 @@
         <v>6</v>
       </c>
       <c r="AD68" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AE68" t="n">
         <v>19.01586724053946</v>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="n">
-        <v>2.777777777777778</v>
+        <v>56.09756097560975</v>
       </c>
       <c r="N69" t="n">
         <v>70</v>
@@ -7647,37 +7647,37 @@
         <v>361.7142857142857</v>
       </c>
       <c r="T69" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U69" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="V69" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W69" t="n">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC69" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AD69" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="AE69" t="n">
         <v>19.77269836258305</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
-        <v>14.70588235294118</v>
+        <v>60</v>
       </c>
       <c r="N70" t="n">
         <v>16.35714285714286</v>
@@ -7758,34 +7758,34 @@
         <v>7</v>
       </c>
       <c r="U70" t="n">
+        <v>6</v>
+      </c>
+      <c r="V70" t="n">
         <v>9</v>
       </c>
-      <c r="V70" t="n">
-        <v>8</v>
-      </c>
       <c r="W70" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="X70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA70" t="n">
         <v>3</v>
       </c>
       <c r="AB70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD70" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE70" t="n">
         <v>14.0927735385985</v>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="n">
-        <v>23.63636363636364</v>
+        <v>64.86486486486487</v>
       </c>
       <c r="N71" t="n">
         <v>24.07142857142857</v>
@@ -7866,34 +7866,34 @@
         <v>14</v>
       </c>
       <c r="U71" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V71" t="n">
         <v>15</v>
       </c>
       <c r="W71" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="X71" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA71" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB71" t="n">
         <v>7</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>3</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
       </c>
       <c r="AD71" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AE71" t="n">
         <v>18.36866430209702</v>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="n">
-        <v>23.68421052631579</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="N72" t="n">
         <v>10.28571428571429</v>
@@ -7974,16 +7974,16 @@
         <v>8</v>
       </c>
       <c r="U72" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V72" t="n">
         <v>11</v>
       </c>
       <c r="W72" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="X72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y72" t="n">
         <v>2</v>
@@ -7992,16 +7992,16 @@
         <v>2</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD72" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE72" t="n">
         <v>19.98591870008162</v>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
-        <v>24.24242424242424</v>
+        <v>69.56521739130434</v>
       </c>
       <c r="N73" t="n">
         <v>16.21428571428572</v>
@@ -8082,22 +8082,22 @@
         <v>7</v>
       </c>
       <c r="U73" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V73" t="n">
         <v>7</v>
       </c>
       <c r="W73" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y73" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z73" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -8109,7 +8109,7 @@
         <v>6</v>
       </c>
       <c r="AD73" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AE73" t="n">
         <v>13.50248228493588</v>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="n">
-        <v>30.76923076923077</v>
+        <v>72.22222222222223</v>
       </c>
       <c r="N74" t="n">
         <v>5.428571428571429</v>
@@ -8187,22 +8187,22 @@
         <v>374.3571428571429</v>
       </c>
       <c r="T74" t="n">
+        <v>7</v>
+      </c>
+      <c r="U74" t="n">
+        <v>5</v>
+      </c>
+      <c r="V74" t="n">
         <v>8</v>
       </c>
-      <c r="U74" t="n">
-        <v>6</v>
-      </c>
-      <c r="V74" t="n">
-        <v>9</v>
-      </c>
       <c r="W74" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="X74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z74" t="n">
         <v>3</v>
@@ -8211,13 +8211,13 @@
         <v>1</v>
       </c>
       <c r="AB74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD74" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE74" t="n">
         <v>15.11465886751754</v>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="n">
-        <v>21.05263157894737</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N75" t="n">
         <v>28</v>
@@ -8295,16 +8295,16 @@
         <v>382.5</v>
       </c>
       <c r="T75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V75" t="n">
         <v>6</v>
       </c>
       <c r="W75" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="X75" t="n">
         <v>0</v>
@@ -8313,7 +8313,7 @@
         <v>3</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -8322,10 +8322,10 @@
         <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD75" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE75" t="n">
         <v>10.95640337169131</v>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="n">
-        <v>37.5</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N76" t="n">
         <v>0</v>
@@ -8409,10 +8409,10 @@
         <v>3</v>
       </c>
       <c r="V76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X76" t="n">
         <v>2</v>
@@ -8424,16 +8424,16 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC76" t="n">
         <v>0</v>
       </c>
-      <c r="AB76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>1</v>
-      </c>
       <c r="AD76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE76" t="n">
         <v>12.01033023635079</v>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="n">
-        <v>31.70731707317073</v>
+        <v>76.66666666666667</v>
       </c>
       <c r="N77" t="n">
         <v>4.928571428571429</v>
@@ -8514,34 +8514,34 @@
         <v>11</v>
       </c>
       <c r="U77" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V77" t="n">
         <v>10</v>
       </c>
       <c r="W77" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="X77" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y77" t="n">
         <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB77" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD77" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AE77" t="n">
         <v>20.12887015524176</v>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
-        <v>37.5</v>
+        <v>70.83333333333333</v>
       </c>
       <c r="N78" t="n">
         <v>4.214285714285714</v>
@@ -8619,37 +8619,37 @@
         <v>377.1428571428571</v>
       </c>
       <c r="T78" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U78" t="n">
+        <v>9</v>
+      </c>
+      <c r="V78" t="n">
         <v>10</v>
       </c>
-      <c r="V78" t="n">
-        <v>11</v>
-      </c>
       <c r="W78" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="X78" t="n">
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z78" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC78" t="n">
         <v>4</v>
       </c>
-      <c r="AA78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC78" t="n">
-        <v>3</v>
-      </c>
       <c r="AD78" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AE78" t="n">
         <v>16.69520106736639</v>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="n">
-        <v>2.702702702702703</v>
+        <v>55</v>
       </c>
       <c r="N79" t="n">
         <v>60.42857142857143</v>
@@ -8730,34 +8730,34 @@
         <v>9</v>
       </c>
       <c r="U79" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V79" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W79" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD79" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AE79" t="n">
         <v>13.23954172203712</v>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="n">
-        <v>8.333333333333334</v>
+        <v>31.25</v>
       </c>
       <c r="N80" t="n">
         <v>7.714285714285714</v>
@@ -8838,19 +8838,19 @@
         <v>6</v>
       </c>
       <c r="U80" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W80" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z80" t="n">
         <v>0</v>
@@ -8862,10 +8862,10 @@
         <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD80" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE80" t="n">
         <v>10.89180027346899</v>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="n">
-        <v>15.15151515151515</v>
+        <v>50</v>
       </c>
       <c r="N81" t="n">
         <v>15</v>
@@ -8946,34 +8946,34 @@
         <v>9</v>
       </c>
       <c r="U81" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V81" t="n">
         <v>7</v>
       </c>
       <c r="W81" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z81" t="n">
         <v>2</v>
       </c>
       <c r="AA81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC81" t="n">
         <v>1</v>
       </c>
       <c r="AD81" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE81" t="n">
         <v>13.84832189161534</v>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="n">
-        <v>9.23076923076923</v>
+        <v>63.41463414634146</v>
       </c>
       <c r="N82" t="n">
         <v>30</v>
@@ -9054,34 +9054,34 @@
         <v>15</v>
       </c>
       <c r="U82" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="V82" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W82" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="X82" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z82" t="n">
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AB82" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="AE82" t="n">
         <v>20.88240828348332</v>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="n">
-        <v>60.46511627906977</v>
+        <v>72.97297297297297</v>
       </c>
       <c r="N83" t="n">
         <v>7.142857142857143</v>
@@ -9162,19 +9162,19 @@
         <v>13</v>
       </c>
       <c r="U83" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V83" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W83" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="X83" t="n">
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z83" t="n">
         <v>9</v>
@@ -9189,7 +9189,7 @@
         <v>9</v>
       </c>
       <c r="AD83" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE83" t="n">
         <v>41.28298099818006</v>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="n">
-        <v>27.90697674418605</v>
+        <v>55.88235294117647</v>
       </c>
       <c r="N84" t="n">
         <v>7.928571428571429</v>
@@ -9273,22 +9273,22 @@
         <v>12</v>
       </c>
       <c r="V84" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W84" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="X84" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y84" t="n">
         <v>3</v>
       </c>
       <c r="Z84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA84" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB84" t="n">
         <v>4</v>
@@ -9297,7 +9297,7 @@
         <v>1</v>
       </c>
       <c r="AD84" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AE84" t="n">
         <v>16.58474761856769</v>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="n">
-        <v>10.63829787234043</v>
+        <v>48.38709677419355</v>
       </c>
       <c r="N85" t="n">
         <v>11.07142857142857</v>
@@ -9375,37 +9375,37 @@
         <v>378.5714285714286</v>
       </c>
       <c r="T85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U85" t="n">
+        <v>14</v>
+      </c>
+      <c r="V85" t="n">
+        <v>11</v>
+      </c>
+      <c r="W85" t="n">
+        <v>31</v>
+      </c>
+      <c r="X85" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD85" t="n">
         <v>15</v>
-      </c>
-      <c r="V85" t="n">
-        <v>12</v>
-      </c>
-      <c r="W85" t="n">
-        <v>47</v>
-      </c>
-      <c r="X85" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB85" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC85" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD85" t="n">
-        <v>5</v>
       </c>
       <c r="AE85" t="n">
         <v>15.60326911093764</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="n">
-        <v>24.07407407407407</v>
+        <v>58.53658536585366</v>
       </c>
       <c r="N86" t="n">
         <v>10.85714285714286</v>
@@ -9486,34 +9486,34 @@
         <v>13</v>
       </c>
       <c r="U86" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V86" t="n">
         <v>14</v>
       </c>
       <c r="W86" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="X86" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA86" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB86" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC86" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD86" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AE86" t="n">
         <v>19.62772620104823</v>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="n">
-        <v>24.32432432432432</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N87" t="n">
         <v>8.714285714285714</v>
@@ -9594,16 +9594,16 @@
         <v>9</v>
       </c>
       <c r="U87" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V87" t="n">
         <v>10</v>
       </c>
       <c r="W87" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="X87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y87" t="n">
         <v>1</v>
@@ -9612,16 +9612,16 @@
         <v>2</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC87" t="n">
         <v>2</v>
       </c>
       <c r="AD87" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE87" t="n">
         <v>15.94922353123243</v>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="n">
-        <v>21.42857142857143</v>
+        <v>60.52631578947368</v>
       </c>
       <c r="N88" t="n">
         <v>38.92857142857143</v>
@@ -9702,34 +9702,34 @@
         <v>12</v>
       </c>
       <c r="U88" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V88" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W88" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="X88" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z88" t="n">
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AB88" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD88" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AE88" t="n">
         <v>17.61643901620164</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="n">
-        <v>15</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N89" t="n">
         <v>2.214285714285714</v>
@@ -9810,16 +9810,16 @@
         <v>6</v>
       </c>
       <c r="U89" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V89" t="n">
         <v>5</v>
       </c>
       <c r="W89" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="X89" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y89" t="n">
         <v>0</v>
@@ -9828,16 +9828,16 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC89" t="n">
         <v>1</v>
       </c>
       <c r="AD89" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AE89" t="n">
         <v>12.05521174707967</v>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="n">
-        <v>3.773584905660377</v>
+        <v>51.72413793103448</v>
       </c>
       <c r="N90" t="n">
         <v>23.71428571428572</v>
@@ -9915,37 +9915,37 @@
         <v>373.4285714285714</v>
       </c>
       <c r="T90" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="U90" t="n">
         <v>12</v>
       </c>
       <c r="V90" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W90" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="X90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD90" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="AE90" t="n">
         <v>16.56399536931215</v>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="n">
-        <v>16.12903225806452</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N91" t="n">
         <v>11.6</v>
@@ -10023,37 +10023,37 @@
         <v>356.9333333333333</v>
       </c>
       <c r="T91" t="n">
+        <v>5</v>
+      </c>
+      <c r="U91" t="n">
+        <v>9</v>
+      </c>
+      <c r="V91" t="n">
         <v>6</v>
       </c>
-      <c r="U91" t="n">
-        <v>11</v>
-      </c>
-      <c r="V91" t="n">
-        <v>7</v>
-      </c>
       <c r="W91" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="X91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y91" t="n">
         <v>2</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA91" t="n">
         <v>1</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD91" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE91" t="n">
         <v>13.97923069988003</v>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="n">
-        <v>14.8936170212766</v>
+        <v>76.66666666666667</v>
       </c>
       <c r="N92" t="n">
         <v>16.81818181818182</v>
@@ -10134,34 +10134,34 @@
         <v>12</v>
       </c>
       <c r="U92" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V92" t="n">
         <v>11</v>
       </c>
       <c r="W92" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="X92" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA92" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AB92" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD92" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AE92" t="n">
         <v>16.38946371419834</v>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="n">
-        <v>16.3265306122449</v>
+        <v>61.76470588235294</v>
       </c>
       <c r="N93" t="n">
         <v>30.64285714285714</v>
@@ -10245,31 +10245,31 @@
         <v>10</v>
       </c>
       <c r="V93" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W93" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="X93" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z93" t="n">
         <v>1</v>
       </c>
       <c r="AA93" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AB93" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD93" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AE93" t="n">
         <v>16.63993026195233</v>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="n">
-        <v>41.53846153846154</v>
+        <v>54.3859649122807</v>
       </c>
       <c r="N94" t="n">
         <v>3.571428571428572</v>
@@ -10350,34 +10350,34 @@
         <v>15</v>
       </c>
       <c r="U94" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V94" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="W94" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="X94" t="n">
         <v>10</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z94" t="n">
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
       </c>
       <c r="AD94" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="AE94" t="n">
         <v>26.0885837133541</v>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="n">
-        <v>22.5</v>
+        <v>54.3859649122807</v>
       </c>
       <c r="N95" t="n">
         <v>16.66666666666667</v>
@@ -10458,34 +10458,34 @@
         <v>20</v>
       </c>
       <c r="U95" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V95" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="W95" t="n">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="X95" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC95" t="n">
         <v>5</v>
       </c>
-      <c r="Y95" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA95" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB95" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC95" t="n">
-        <v>3</v>
-      </c>
       <c r="AD95" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="AE95" t="n">
         <v>29.2742701899954</v>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="n">
-        <v>24.28571428571428</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="N96" t="n">
         <v>55.5</v>
@@ -10563,37 +10563,37 @@
         <v>374.7500000000001</v>
       </c>
       <c r="T96" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U96" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="V96" t="n">
         <v>16</v>
       </c>
       <c r="W96" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z96" t="n">
         <v>4</v>
       </c>
       <c r="AA96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC96" t="n">
         <v>7</v>
       </c>
       <c r="AD96" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AE96" t="n">
         <v>21.58422575563188</v>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="n">
-        <v>32.46753246753246</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N97" t="n">
         <v>13.06666666666667</v>
@@ -10671,37 +10671,37 @@
         <v>356.6666666666667</v>
       </c>
       <c r="T97" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U97" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="V97" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W97" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="X97" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y97" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z97" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA97" t="n">
         <v>4</v>
       </c>
       <c r="AB97" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC97" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AD97" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="AE97" t="n">
         <v>34.25182764904322</v>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="n">
-        <v>7.407407407407407</v>
+        <v>50</v>
       </c>
       <c r="N98" t="n">
         <v>22.83333333333333</v>
@@ -10782,34 +10782,34 @@
         <v>3</v>
       </c>
       <c r="U98" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V98" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W98" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="X98" t="n">
         <v>1</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC98" t="n">
         <v>1</v>
       </c>
       <c r="AD98" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE98" t="n">
         <v>9.286118635600578</v>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="n">
-        <v>14.28571428571429</v>
+        <v>50</v>
       </c>
       <c r="N99" t="n">
         <v>18.92857142857143</v>
@@ -10890,34 +10890,34 @@
         <v>6</v>
       </c>
       <c r="U99" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V99" t="n">
         <v>6</v>
       </c>
       <c r="W99" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="X99" t="n">
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD99" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE99" t="n">
         <v>10.68893004378599</v>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="n">
-        <v>2.857142857142857</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="N100" t="n">
         <v>35.21428571428572</v>
@@ -10995,7 +10995,7 @@
         <v>362.7857142857143</v>
       </c>
       <c r="T100" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U100" t="n">
         <v>10</v>
@@ -11004,28 +11004,28 @@
         <v>7</v>
       </c>
       <c r="W100" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="X100" t="n">
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
       </c>
       <c r="AD100" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AE100" t="n">
         <v>14.4361662086699</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="n">
-        <v>9.523809523809524</v>
+        <v>80.76923076923077</v>
       </c>
       <c r="N101" t="n">
         <v>46.07142857142857</v>
@@ -11103,7 +11103,7 @@
         <v>368.2142857142857</v>
       </c>
       <c r="T101" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U101" t="n">
         <v>10</v>
@@ -11112,28 +11112,28 @@
         <v>9</v>
       </c>
       <c r="W101" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="X101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y101" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z101" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC101" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD101" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="AE101" t="n">
         <v>15.77662171136436</v>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="n">
-        <v>20.68965517241379</v>
+        <v>80</v>
       </c>
       <c r="N102" t="n">
         <v>7.9</v>
@@ -11214,34 +11214,34 @@
         <v>6</v>
       </c>
       <c r="U102" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V102" t="n">
         <v>7</v>
       </c>
       <c r="W102" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="X102" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA102" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AB102" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC102" t="n">
         <v>2</v>
       </c>
       <c r="AD102" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AE102" t="n">
         <v>11.33468199901741</v>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="n">
-        <v>38.23529411764706</v>
+        <v>80</v>
       </c>
       <c r="N103" t="n">
         <v>8</v>
@@ -11322,16 +11322,16 @@
         <v>7</v>
       </c>
       <c r="U103" t="n">
+        <v>9</v>
+      </c>
+      <c r="V103" t="n">
         <v>11</v>
       </c>
-      <c r="V103" t="n">
-        <v>12</v>
-      </c>
       <c r="W103" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="X103" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y103" t="n">
         <v>1</v>
@@ -11340,16 +11340,16 @@
         <v>1</v>
       </c>
       <c r="AA103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB103" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC103" t="n">
         <v>1</v>
       </c>
       <c r="AD103" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AE103" t="n">
         <v>12.65154985140382</v>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="n">
-        <v>16.66666666666667</v>
+        <v>50</v>
       </c>
       <c r="N104" t="n">
         <v>11.55555555555556</v>
@@ -11430,16 +11430,16 @@
         <v>4</v>
       </c>
       <c r="U104" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V104" t="n">
         <v>5</v>
       </c>
       <c r="W104" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="X104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y104" t="n">
         <v>0</v>
@@ -11448,16 +11448,16 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB104" t="n">
         <v>1</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD104" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE104" t="n">
         <v>9.501222448606384</v>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="n">
-        <v>10.71428571428571</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="N105" t="n">
         <v>9.642857142857142</v>
@@ -11538,34 +11538,34 @@
         <v>4</v>
       </c>
       <c r="U105" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V105" t="n">
         <v>7</v>
       </c>
       <c r="W105" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="X105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y105" t="n">
         <v>1</v>
       </c>
       <c r="Z105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
       </c>
       <c r="AD105" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE105" t="n">
         <v>12.17403470204763</v>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="n">
-        <v>14.63414634146342</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N106" t="n">
         <v>24.9</v>
@@ -11646,34 +11646,34 @@
         <v>9</v>
       </c>
       <c r="U106" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V106" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W106" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="X106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD106" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AE106" t="n">
         <v>15.76769351501721</v>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="n">
-        <v>19.14893617021277</v>
+        <v>65.51724137931035</v>
       </c>
       <c r="N107" t="n">
         <v>39.35714285714285</v>
@@ -11751,37 +11751,37 @@
         <v>373.8571428571428</v>
       </c>
       <c r="T107" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U107" t="n">
         <v>11</v>
       </c>
       <c r="V107" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W107" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="X107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y107" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z107" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB107" t="n">
         <v>1</v>
       </c>
       <c r="AC107" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD107" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AE107" t="n">
         <v>15.06925879665454</v>
@@ -11838,7 +11838,7 @@
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="n">
-        <v>12.5</v>
+        <v>65.625</v>
       </c>
       <c r="N108" t="n">
         <v>32.21428571428572</v>
@@ -11862,34 +11862,34 @@
         <v>10</v>
       </c>
       <c r="U108" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V108" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W108" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="X108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z108" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC108" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD108" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="AE108" t="n">
         <v>16.75038722937033</v>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="n">
-        <v>16</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N109" t="n">
         <v>9.333333333333334</v>
@@ -11967,25 +11967,25 @@
         <v>356.1333333333333</v>
       </c>
       <c r="T109" t="n">
+        <v>7</v>
+      </c>
+      <c r="U109" t="n">
         <v>8</v>
-      </c>
-      <c r="U109" t="n">
-        <v>9</v>
       </c>
       <c r="V109" t="n">
         <v>4</v>
       </c>
       <c r="W109" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="X109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -11994,10 +11994,10 @@
         <v>0</v>
       </c>
       <c r="AC109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD109" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE109" t="n">
         <v>11.52061446149812</v>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="n">
-        <v>35.71428571428572</v>
+        <v>77.41935483870968</v>
       </c>
       <c r="N110" t="n">
         <v>17.71428571428572</v>
@@ -12081,31 +12081,31 @@
         <v>10</v>
       </c>
       <c r="V110" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W110" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="X110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y110" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z110" t="n">
         <v>5</v>
       </c>
       <c r="AA110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC110" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD110" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AE110" t="n">
         <v>17.89191897124594</v>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="n">
-        <v>21.21212121212121</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N111" t="n">
         <v>40.78571428571428</v>
@@ -12186,34 +12186,34 @@
         <v>8</v>
       </c>
       <c r="U111" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V111" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W111" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="X111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD111" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AE111" t="n">
         <v>11.82476977002612</v>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="n">
-        <v>16.66666666666667</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N112" t="n">
         <v>23.42857142857143</v>
@@ -12294,34 +12294,34 @@
         <v>3</v>
       </c>
       <c r="U112" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V112" t="n">
+        <v>6</v>
+      </c>
+      <c r="W112" t="n">
+        <v>13</v>
+      </c>
+      <c r="X112" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD112" t="n">
         <v>7</v>
-      </c>
-      <c r="W112" t="n">
-        <v>24</v>
-      </c>
-      <c r="X112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y112" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z112" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB112" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC112" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD112" t="n">
-        <v>4</v>
       </c>
       <c r="AE112" t="n">
         <v>8.580171273220284</v>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="n">
-        <v>6.25</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="N113" t="n">
         <v>10.26666666666667</v>
@@ -12402,34 +12402,34 @@
         <v>4</v>
       </c>
       <c r="U113" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V113" t="n">
         <v>4</v>
       </c>
       <c r="W113" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="X113" t="n">
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z113" t="n">
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
       </c>
       <c r="AD113" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE113" t="n">
         <v>7.105960855900688</v>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="n">
-        <v>25.92592592592593</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N114" t="n">
         <v>54.71428571428572</v>
@@ -12507,37 +12507,37 @@
         <v>359.2857142857143</v>
       </c>
       <c r="T114" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U114" t="n">
         <v>6</v>
       </c>
       <c r="V114" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W114" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="X114" t="n">
         <v>2</v>
       </c>
       <c r="Y114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB114" t="n">
         <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD114" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE114" t="n">
         <v>11.50801214193721</v>
@@ -12594,7 +12594,7 @@
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="n">
-        <v>12.12121212121212</v>
+        <v>55</v>
       </c>
       <c r="N115" t="n">
         <v>19</v>
@@ -12618,34 +12618,34 @@
         <v>7</v>
       </c>
       <c r="U115" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V115" t="n">
         <v>9</v>
       </c>
       <c r="W115" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="X115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC115" t="n">
         <v>2</v>
       </c>
       <c r="AD115" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AE115" t="n">
         <v>11.99792432369465</v>
@@ -12702,7 +12702,7 @@
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="n">
-        <v>14.28571428571429</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N116" t="n">
         <v>7</v>
@@ -12726,16 +12726,16 @@
         <v>5</v>
       </c>
       <c r="U116" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V116" t="n">
         <v>6</v>
       </c>
       <c r="W116" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="X116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y116" t="n">
         <v>1</v>
@@ -12744,16 +12744,16 @@
         <v>1</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC116" t="n">
         <v>1</v>
       </c>
       <c r="AD116" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE116" t="n">
         <v>10.12144238271243</v>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="n">
-        <v>9.67741935483871</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="N117" t="n">
         <v>19.85714285714286</v>
@@ -12831,37 +12831,37 @@
         <v>382.8571428571429</v>
       </c>
       <c r="T117" t="n">
+        <v>6</v>
+      </c>
+      <c r="U117" t="n">
         <v>7</v>
-      </c>
-      <c r="U117" t="n">
-        <v>8</v>
       </c>
       <c r="V117" t="n">
         <v>8</v>
       </c>
       <c r="W117" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="X117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD117" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AE117" t="n">
         <v>11.40574153172862</v>
@@ -12918,7 +12918,7 @@
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="n">
-        <v>6.25</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="N118" t="n">
         <v>40.55555555555556</v>
@@ -12945,31 +12945,31 @@
         <v>7</v>
       </c>
       <c r="V118" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W118" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="X118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y118" t="n">
         <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD118" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE118" t="n">
         <v>11.17272301948955</v>
@@ -13026,7 +13026,7 @@
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="n">
-        <v>15.78947368421053</v>
+        <v>75</v>
       </c>
       <c r="N119" t="n">
         <v>3.857142857142857</v>
@@ -13047,37 +13047,37 @@
         <v>376.6428571428571</v>
       </c>
       <c r="T119" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U119" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V119" t="n">
         <v>4</v>
       </c>
       <c r="W119" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="X119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y119" t="n">
         <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD119" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AE119" t="n">
         <v>12.50332360506581</v>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="n">
-        <v>15.90909090909091</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N120" t="n">
         <v>16.76923076923077</v>
@@ -13158,34 +13158,34 @@
         <v>11</v>
       </c>
       <c r="U120" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V120" t="n">
         <v>9</v>
       </c>
       <c r="W120" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="X120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA120" t="n">
         <v>3</v>
       </c>
       <c r="AB120" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD120" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE120" t="n">
         <v>15.84464162278841</v>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="n">
-        <v>8.695652173913043</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="N121" t="n">
         <v>45.14285714285715</v>
@@ -13266,19 +13266,19 @@
         <v>6</v>
       </c>
       <c r="U121" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V121" t="n">
         <v>4</v>
       </c>
       <c r="W121" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="X121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z121" t="n">
         <v>0</v>
@@ -13290,10 +13290,10 @@
         <v>0</v>
       </c>
       <c r="AC121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD121" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE121" t="n">
         <v>9.851558503985425</v>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="n">
-        <v>23.63636363636364</v>
+        <v>56.41025641025641</v>
       </c>
       <c r="N122" t="n">
         <v>13.45454545454546</v>
@@ -13374,34 +13374,34 @@
         <v>12</v>
       </c>
       <c r="U122" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V122" t="n">
         <v>13</v>
       </c>
       <c r="W122" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="X122" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z122" t="n">
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AB122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC122" t="n">
         <v>3</v>
       </c>
       <c r="AD122" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AE122" t="n">
         <v>17.14660030621432</v>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="n">
-        <v>28.2051282051282</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N123" t="n">
         <v>9</v>
@@ -13482,34 +13482,34 @@
         <v>9</v>
       </c>
       <c r="U123" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V123" t="n">
         <v>11</v>
       </c>
       <c r="W123" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="X123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y123" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD123" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AE123" t="n">
         <v>15.29708560850937</v>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="n">
-        <v>9.25925925925926</v>
+        <v>67.74193548387096</v>
       </c>
       <c r="N124" t="n">
         <v>30.5</v>
@@ -13590,34 +13590,34 @@
         <v>9</v>
       </c>
       <c r="U124" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V124" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W124" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="X124" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y124" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB124" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC124" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD124" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AE124" t="n">
         <v>14.39449815963401</v>
@@ -13674,7 +13674,7 @@
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="n">
-        <v>15.625</v>
+        <v>48</v>
       </c>
       <c r="N125" t="n">
         <v>12.33333333333333</v>
@@ -13698,34 +13698,34 @@
         <v>5</v>
       </c>
       <c r="U125" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V125" t="n">
         <v>11</v>
       </c>
       <c r="W125" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="X125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y125" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB125" t="n">
         <v>0</v>
       </c>
       <c r="AC125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD125" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE125" t="n">
         <v>11.59205332970346</v>
@@ -13782,7 +13782,7 @@
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="n">
-        <v>10.52631578947368</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N126" t="n">
         <v>12.07692307692308</v>
@@ -13803,37 +13803,37 @@
         <v>371.6923076923077</v>
       </c>
       <c r="T126" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U126" t="n">
         <v>16</v>
       </c>
       <c r="V126" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W126" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="X126" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA126" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC126" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD126" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AE126" t="n">
         <v>18.07369088562876</v>
@@ -13890,7 +13890,7 @@
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N127" t="n">
         <v>30.42857142857143</v>
@@ -13914,34 +13914,34 @@
         <v>4</v>
       </c>
       <c r="U127" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V127" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W127" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="X127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD127" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AE127" t="n">
         <v>10.45965000921505</v>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="n">
-        <v>15.15151515151515</v>
+        <v>68.18181818181819</v>
       </c>
       <c r="N128" t="n">
         <v>10</v>
@@ -14019,37 +14019,37 @@
         <v>366.1111111111111</v>
       </c>
       <c r="T128" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U128" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V128" t="n">
         <v>6</v>
       </c>
       <c r="W128" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="X128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD128" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AE128" t="n">
         <v>12.85463380130124</v>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="n">
-        <v>21.05263157894737</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="N129" t="n">
         <v>8.357142857142858</v>
@@ -14133,22 +14133,22 @@
         <v>6</v>
       </c>
       <c r="V129" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W129" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="X129" t="n">
         <v>1</v>
       </c>
       <c r="Y129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z129" t="n">
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB129" t="n">
         <v>1</v>
@@ -14157,7 +14157,7 @@
         <v>0</v>
       </c>
       <c r="AD129" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE129" t="n">
         <v>13.311208460562</v>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="n">
-        <v>30.3030303030303</v>
+        <v>73.91304347826087</v>
       </c>
       <c r="N130" t="n">
         <v>28.85714285714286</v>
@@ -14235,37 +14235,37 @@
         <v>390.5714285714286</v>
       </c>
       <c r="T130" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U130" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V130" t="n">
         <v>7</v>
       </c>
       <c r="W130" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="X130" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z130" t="n">
         <v>2</v>
       </c>
       <c r="AA130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB130" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD130" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE130" t="n">
         <v>13.797678823224</v>
@@ -14322,7 +14322,7 @@
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="n">
-        <v>18.18181818181818</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N131" t="n">
         <v>20</v>
@@ -14346,34 +14346,34 @@
         <v>5</v>
       </c>
       <c r="U131" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V131" t="n">
         <v>6</v>
       </c>
       <c r="W131" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="X131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
       </c>
       <c r="AD131" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AE131" t="n">
         <v>10.06200468779238</v>
@@ -14430,7 +14430,7 @@
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="n">
-        <v>16.66666666666667</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="N132" t="n">
         <v>4</v>
@@ -14454,16 +14454,16 @@
         <v>4</v>
       </c>
       <c r="U132" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V132" t="n">
         <v>9</v>
       </c>
       <c r="W132" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="X132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y132" t="n">
         <v>1</v>
@@ -14472,16 +14472,16 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC132" t="n">
         <v>1</v>
       </c>
       <c r="AD132" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE132" t="n">
         <v>10.76592164756172</v>
@@ -14538,7 +14538,7 @@
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="n">
-        <v>22.22222222222222</v>
+        <v>76</v>
       </c>
       <c r="N133" t="n">
         <v>16.64285714285714</v>
@@ -14559,37 +14559,37 @@
         <v>384.2857142857143</v>
       </c>
       <c r="T133" t="n">
+        <v>9</v>
+      </c>
+      <c r="U133" t="n">
         <v>10</v>
-      </c>
-      <c r="U133" t="n">
-        <v>11</v>
       </c>
       <c r="V133" t="n">
         <v>8</v>
       </c>
       <c r="W133" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="X133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y133" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z133" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC133" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD133" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AE133" t="n">
         <v>16.11060642809712</v>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="n">
-        <v>28.57142857142857</v>
+        <v>65.38461538461539</v>
       </c>
       <c r="N134" t="n">
         <v>3.615384615384615</v>
@@ -14670,34 +14670,34 @@
         <v>9</v>
       </c>
       <c r="U134" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V134" t="n">
         <v>10</v>
       </c>
       <c r="W134" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="X134" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y134" t="n">
         <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB134" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC134" t="n">
         <v>2</v>
       </c>
       <c r="AD134" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE134" t="n">
         <v>15.10665999126453</v>
@@ -14754,7 +14754,7 @@
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="n">
-        <v>9.67741935483871</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N135" t="n">
         <v>44.57142857142857</v>
@@ -14778,34 +14778,34 @@
         <v>9</v>
       </c>
       <c r="U135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W135" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="X135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA135" t="n">
         <v>1</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC135" t="n">
         <v>2</v>
       </c>
       <c r="AD135" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AE135" t="n">
         <v>11.85349911420817</v>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="n">
-        <v>28.30188679245283</v>
+        <v>64.1025641025641</v>
       </c>
       <c r="N136" t="n">
         <v>21</v>
@@ -14886,34 +14886,34 @@
         <v>14</v>
       </c>
       <c r="U136" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V136" t="n">
         <v>16</v>
       </c>
       <c r="W136" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="X136" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA136" t="n">
         <v>4</v>
       </c>
       <c r="AB136" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC136" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD136" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AE136" t="n">
         <v>17.90480886409047</v>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="n">
-        <v>7.936507936507937</v>
+        <v>55</v>
       </c>
       <c r="N137" t="n">
         <v>28.5</v>
@@ -14991,37 +14991,37 @@
         <v>370.7142857142857</v>
       </c>
       <c r="T137" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U137" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V137" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W137" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="X137" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y137" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z137" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC137" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AD137" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="AE137" t="n">
         <v>18.58565914401932</v>
@@ -15078,7 +15078,7 @@
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="n">
-        <v>37.5</v>
+        <v>72</v>
       </c>
       <c r="N138" t="n">
         <v>12.15384615384615</v>
@@ -15102,22 +15102,22 @@
         <v>6</v>
       </c>
       <c r="U138" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V138" t="n">
         <v>10</v>
       </c>
       <c r="W138" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="X138" t="n">
         <v>0</v>
       </c>
       <c r="Y138" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z138" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA138" t="n">
         <v>0</v>
@@ -15126,10 +15126,10 @@
         <v>0</v>
       </c>
       <c r="AC138" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AD138" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AE138" t="n">
         <v>13.80781851062432</v>
@@ -15186,7 +15186,7 @@
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="n">
-        <v>17.64705882352941</v>
+        <v>65</v>
       </c>
       <c r="N139" t="n">
         <v>26.57142857142857</v>
@@ -15210,34 +15210,34 @@
         <v>8</v>
       </c>
       <c r="U139" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V139" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W139" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="X139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z139" t="n">
         <v>3</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD139" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE139" t="n">
         <v>14.07025075976412</v>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="n">
-        <v>23.52941176470588</v>
+        <v>61.22448979591837</v>
       </c>
       <c r="N140" t="n">
         <v>21.2</v>
@@ -15318,34 +15318,34 @@
         <v>17</v>
       </c>
       <c r="U140" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V140" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="W140" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="X140" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y140" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z140" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC140" t="n">
         <v>4</v>
       </c>
-      <c r="AA140" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB140" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC140" t="n">
-        <v>1</v>
-      </c>
       <c r="AD140" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AE140" t="n">
         <v>20.01371162345026</v>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="n">
-        <v>5.769230769230769</v>
+        <v>70</v>
       </c>
       <c r="N141" t="n">
         <v>45.14285714285715</v>
@@ -15426,34 +15426,34 @@
         <v>12</v>
       </c>
       <c r="U141" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V141" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W141" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="X141" t="n">
         <v>1</v>
       </c>
       <c r="Y141" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z141" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB141" t="n">
         <v>1</v>
       </c>
       <c r="AC141" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD141" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="AE141" t="n">
         <v>17.19083751689092</v>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="n">
-        <v>19.56521739130435</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="N142" t="n">
         <v>27.875</v>
@@ -15531,37 +15531,37 @@
         <v>371.5</v>
       </c>
       <c r="T142" t="n">
+        <v>9</v>
+      </c>
+      <c r="U142" t="n">
         <v>11</v>
-      </c>
-      <c r="U142" t="n">
-        <v>14</v>
       </c>
       <c r="V142" t="n">
         <v>10</v>
       </c>
       <c r="W142" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="X142" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA142" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB142" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC142" t="n">
         <v>1</v>
       </c>
       <c r="AD142" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="AE142" t="n">
         <v>15.11003627660977</v>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="n">
-        <v>50</v>
+        <v>91.66666666666667</v>
       </c>
       <c r="N143" t="n">
         <v>5.733333333333333</v>
@@ -15642,16 +15642,16 @@
         <v>4</v>
       </c>
       <c r="U143" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V143" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W143" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="X143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y143" t="n">
         <v>0</v>
@@ -15663,13 +15663,13 @@
         <v>3</v>
       </c>
       <c r="AB143" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
       </c>
       <c r="AD143" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE143" t="n">
         <v>10.39647478285796</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="n">
-        <v>4.761904761904762</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N144" t="n">
         <v>10.625</v>
@@ -15753,19 +15753,19 @@
         <v>7</v>
       </c>
       <c r="V144" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W144" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="X144" t="n">
         <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z144" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA144" t="n">
         <v>0</v>
@@ -15774,10 +15774,10 @@
         <v>0</v>
       </c>
       <c r="AC144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD144" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AE144" t="n">
         <v>9.487477610064012</v>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="n">
-        <v>41.1764705882353</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N145" t="n">
         <v>2.571428571428572</v>
@@ -15858,19 +15858,19 @@
         <v>4</v>
       </c>
       <c r="U145" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V145" t="n">
         <v>7</v>
       </c>
       <c r="W145" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="X145" t="n">
         <v>1</v>
       </c>
       <c r="Y145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z145" t="n">
         <v>2</v>
@@ -15885,7 +15885,7 @@
         <v>3</v>
       </c>
       <c r="AD145" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE145" t="n">
         <v>10.99868223237499</v>
@@ -15942,7 +15942,7 @@
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="n">
-        <v>13.33333333333333</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="N146" t="n">
         <v>18.66666666666667</v>
@@ -15972,16 +15972,16 @@
         <v>5</v>
       </c>
       <c r="W146" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="X146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA146" t="n">
         <v>1</v>
@@ -15990,10 +15990,10 @@
         <v>1</v>
       </c>
       <c r="AC146" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD146" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AE146" t="n">
         <v>12.36033556019622</v>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="n">
-        <v>14.81481481481481</v>
+        <v>50</v>
       </c>
       <c r="N147" t="n">
         <v>27.35714285714286</v>
@@ -16071,7 +16071,7 @@
         <v>380.6428571428572</v>
       </c>
       <c r="T147" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U147" t="n">
         <v>9</v>
@@ -16080,28 +16080,28 @@
         <v>4</v>
       </c>
       <c r="W147" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="X147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z147" t="n">
         <v>1</v>
       </c>
       <c r="AA147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD147" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE147" t="n">
         <v>12.70887128018482</v>
@@ -16158,7 +16158,7 @@
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="n">
-        <v>28.57142857142857</v>
+        <v>56</v>
       </c>
       <c r="N148" t="n">
         <v>21.4</v>
@@ -16182,19 +16182,19 @@
         <v>7</v>
       </c>
       <c r="U148" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V148" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W148" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="X148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z148" t="n">
         <v>4</v>
@@ -16206,10 +16206,10 @@
         <v>1</v>
       </c>
       <c r="AC148" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD148" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AE148" t="n">
         <v>13.61606612077062</v>
@@ -16266,7 +16266,7 @@
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="n">
-        <v>8.163265306122449</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N149" t="n">
         <v>9.133333333333333</v>
@@ -16287,37 +16287,37 @@
         <v>347.8666666666667</v>
       </c>
       <c r="T149" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U149" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V149" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W149" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="X149" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC149" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD149" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AE149" t="n">
         <v>15.37919843413517</v>
@@ -16374,7 +16374,7 @@
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="n">
-        <v>33.33333333333334</v>
+        <v>68.96551724137932</v>
       </c>
       <c r="N150" t="n">
         <v>8.333333333333334</v>
@@ -16395,37 +16395,37 @@
         <v>384.3333333333334</v>
       </c>
       <c r="T150" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U150" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V150" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W150" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="X150" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y150" t="n">
         <v>2</v>
       </c>
       <c r="Z150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA150" t="n">
         <v>3</v>
       </c>
       <c r="AB150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC150" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD150" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AE150" t="n">
         <v>17.00428434398734</v>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="n">
-        <v>31.03448275862069</v>
+        <v>68.18181818181819</v>
       </c>
       <c r="N151" t="n">
         <v>5.928571428571429</v>
@@ -16509,31 +16509,31 @@
         <v>10</v>
       </c>
       <c r="V151" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W151" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="X151" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y151" t="n">
         <v>1</v>
       </c>
       <c r="Z151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC151" t="n">
         <v>3</v>
       </c>
       <c r="AD151" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE151" t="n">
         <v>15.29942703414833</v>
@@ -16590,7 +16590,7 @@
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="n">
-        <v>31.81818181818182</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="N152" t="n">
         <v>9</v>
@@ -16611,7 +16611,7 @@
         <v>385.0833333333334</v>
       </c>
       <c r="T152" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U152" t="n">
         <v>14</v>
@@ -16620,28 +16620,28 @@
         <v>12</v>
       </c>
       <c r="W152" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="X152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y152" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z152" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AA152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC152" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD152" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AE152" t="n">
         <v>16.63698217431</v>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="n">
-        <v>36.11111111111111</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N153" t="n">
         <v>6.428571428571429</v>
@@ -16719,7 +16719,7 @@
         <v>383.2857142857143</v>
       </c>
       <c r="T153" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U153" t="n">
         <v>13</v>
@@ -16728,16 +16728,16 @@
         <v>9</v>
       </c>
       <c r="W153" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="X153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y153" t="n">
         <v>4</v>
       </c>
       <c r="Z153" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA153" t="n">
         <v>1</v>
@@ -16746,10 +16746,10 @@
         <v>1</v>
       </c>
       <c r="AC153" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD153" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE153" t="n">
         <v>15.8676548619318</v>
@@ -16806,7 +16806,7 @@
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="n">
-        <v>8.771929824561404</v>
+        <v>48.64864864864865</v>
       </c>
       <c r="N154" t="n">
         <v>29.46153846153846</v>
@@ -16830,34 +16830,34 @@
         <v>8</v>
       </c>
       <c r="U154" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V154" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W154" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="X154" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB154" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD154" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="AE154" t="n">
         <v>13.89801754410142</v>
@@ -16914,7 +16914,7 @@
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="n">
-        <v>27.27272727272727</v>
+        <v>56</v>
       </c>
       <c r="N155" t="n">
         <v>19.78571428571428</v>
@@ -16938,19 +16938,19 @@
         <v>9</v>
       </c>
       <c r="U155" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V155" t="n">
         <v>7</v>
       </c>
       <c r="W155" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="X155" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z155" t="n">
         <v>1</v>
@@ -16962,10 +16962,10 @@
         <v>1</v>
       </c>
       <c r="AC155" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD155" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AE155" t="n">
         <v>14.04014259230215</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="n">
-        <v>8.163265306122449</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="N156" t="n">
         <v>35.41666666666666</v>
@@ -17046,22 +17046,22 @@
         <v>7</v>
       </c>
       <c r="U156" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V156" t="n">
         <v>12</v>
       </c>
       <c r="W156" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="X156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z156" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA156" t="n">
         <v>0</v>
@@ -17070,10 +17070,10 @@
         <v>0</v>
       </c>
       <c r="AC156" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AD156" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="AE156" t="n">
         <v>15.22216393533114</v>
@@ -17130,7 +17130,7 @@
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="n">
-        <v>5.555555555555555</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="N157" t="n">
         <v>96.42857142857143</v>
@@ -17151,37 +17151,37 @@
         <v>367.2142857142857</v>
       </c>
       <c r="T157" t="n">
+        <v>5</v>
+      </c>
+      <c r="U157" t="n">
+        <v>8</v>
+      </c>
+      <c r="V157" t="n">
         <v>7</v>
       </c>
-      <c r="U157" t="n">
-        <v>9</v>
-      </c>
-      <c r="V157" t="n">
-        <v>8</v>
-      </c>
       <c r="W157" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="X157" t="n">
         <v>0</v>
       </c>
       <c r="Y157" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB157" t="n">
         <v>0</v>
       </c>
       <c r="AC157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD157" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE157" t="n">
         <v>11.62569983711359</v>
